--- a/DATA_DT.xlsx
+++ b/DATA_DT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\dashboard-banhang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB449A8-4C64-4F09-8854-93C59D06181B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1A8C20-84A5-494C-9478-A08D39440A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EAECC936-F02A-47E7-9ACA-F714619D0E74}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
   <si>
     <t>MÌ TRỘN</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>gia_ban</t>
+  </si>
+  <si>
+    <t>banh tráng trộn</t>
   </si>
 </sst>
 </file>
@@ -617,7 +620,7 @@
         <v>46346</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>

--- a/DATA_DT.xlsx
+++ b/DATA_DT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\dashboard-banhang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1A8C20-84A5-494C-9478-A08D39440A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FA03F0-88E3-4C14-9CDD-BE3862F7FEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{EAECC936-F02A-47E7-9ACA-F714619D0E74}"/>
   </bookViews>
@@ -427,6 +427,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E21B136-647D-4C16-B603-34A11B51A5AD}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -464,7 +467,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>46337</v>
+        <v>46272</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -481,7 +484,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>46338</v>
+        <v>46368</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -498,7 +501,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>46339</v>
+        <v>46371</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -532,7 +535,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>46341</v>
+        <v>46371</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -566,7 +569,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>46343</v>
+        <v>46310</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -600,7 +603,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>46345</v>
+        <v>46285</v>
       </c>
       <c r="B11" t="s">
         <v>0</v>
